--- a/data/bets.xlsx
+++ b/data/bets.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,52 +485,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Central Arkansas</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Bellarmine</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>-14.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>+13.1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+4.30</t>
+          <t>+27.10</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Texas +7.0</t>
+          <t>Bellarmine +14.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>164.5</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>169.6</t>
+          <t>131.1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.10</t>
+          <t>-26.90</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -543,201 +543,201 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Notre Dame</t>
+          <t>High Point</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Stanford</t>
+          <t>Gardner Webb</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>-31.5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>-9.6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>+21.90</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>No Bet</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>Gardner Webb +31.5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>146.4</t>
+          <t>133.1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-19.90</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>No Bet</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>Under 153.0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Northwestern</t>
+          <t>Belmont</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Purdue</t>
+          <t>Drake</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+10.5</t>
+          <t>-12.5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+12.5</t>
+          <t>-7.9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+2.00</t>
+          <t>+4.60</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No Bet</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Drake +12.5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>159.4</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12.90</t>
+          <t>-5.20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Over 146.5</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>North Carolina A&amp;T</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>Northeastern</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>+4.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>+4.60</t>
+          <t>+3.60</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USC +6.0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>157.2</t>
+          <t>128.2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.70</t>
+          <t>-24.30</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Over 150.5</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Indiana</t>
+          <t>Winthrop</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Minnesota</t>
+          <t>Charleston Southern</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-5.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-4.4</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>+2.10</t>
+          <t>+0.50</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -748,137 +748,137 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>163.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>151.1</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14.60</t>
+          <t>-21.20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Over 136.5</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>B+</t>
-        </is>
-      </c>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Lipscomb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Baylor</t>
+          <t>Florida Gulf Coast</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-15.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>+1.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>+11.90</t>
+          <t>+5.30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Baylor +15.0</t>
+          <t>Florida Gulf Coast +4.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>163.6</t>
+          <t>135.4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>21.60</t>
+          <t>-15.10</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Over 142.0</t>
+          <t>Under 150.5</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B+</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Butler</t>
+          <t>Murray St.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Creighton</t>
+          <t>Illinois Chicago</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-9.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>+2.40</t>
+          <t>-9.30</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>No Bet</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Murray St. -0.5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>150.2</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-5.30</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -891,152 +891,152 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Austin Peay</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Duquesne</t>
+          <t>Stetson</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>-11.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+7.1</t>
+          <t>+2.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>+9.60</t>
+          <t>+13.80</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Duquesne +2.5</t>
+          <t>Stetson +11.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>A-</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>152.5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>139.4</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>-18.00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>No Bet</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>Under 152.5</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>Chattanooga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>The Citadel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+3.5</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>+8.6</t>
+          <t>+0.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>+5.10</t>
+          <t>+7.90</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>California -3.5</t>
+          <t>The Citadel +7.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>146.9</t>
+          <t>114.9</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-8.60</t>
+          <t>-32.60</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Under 155.5</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UAB</t>
+          <t>Northern Illinois</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>-22.5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-4.6</t>
+          <t>-15.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-6.10</t>
+          <t>+6.80</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Charlotte +1.5</t>
+          <t>Northern Illinois +22.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1046,54 +1046,54 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-11.30</t>
+          <t>-14.70</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Under 145.0</t>
+          <t>Under 155.5</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Davidson</t>
+          <t>UNC Asheville</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Saint Joseph's</t>
+          <t>Longwood</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-1.5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>+0.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>+1.20</t>
+          <t>+1.90</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1104,55 +1104,59 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>140.6</t>
+          <t>128.1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>-12.40</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>No Bet</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>Under 140.5</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>New Mexico</t>
+          <t>Merrimack</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Colorado St.</t>
+          <t>Sacred Heart</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-8.5</t>
+          <t>-8.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>+4.3</t>
+          <t>+6.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>+12.80</t>
+          <t>+14.60</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Colorado St. +8.5</t>
+          <t>Sacred Heart +8.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1162,75 +1166,75 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-11.00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>No Bet</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>Under 141.5</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>Texas St.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>Southern Miss</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-14.5</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-9.2</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>+5.30</t>
+          <t>+0.60</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maryland +14.5</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>C+</t>
-        </is>
-      </c>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>154.9</t>
+          <t>133.9</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>-5.60</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1243,27 +1247,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>La Salle</t>
+          <t>Eastern Michigan</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fordham</t>
+          <t>Bowling Green</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+2.0</t>
+          <t>+4.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>+2.8</t>
+          <t>+3.6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>+0.80</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1274,199 +1278,2199 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-6.50</t>
+          <t>-5.50</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Under 132.0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>George Washington</t>
+          <t>Ball St.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>St. Bonaventure</t>
+          <t>Central Michigan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+nan</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-3.1</t>
+          <t>+11.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>+nan</t>
+          <t>+13.80</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>No Bet</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>Central Michigan +2.0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>125.1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>-8.90</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>No Bet</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>Under 134.0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>North Texas</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Penn</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-7.5</t>
+          <t>+2.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>+8.7</t>
+          <t>+9.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>+16.20</t>
+          <t>+7.20</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rice +7.5</t>
+          <t>Penn -2.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>135.4</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-9.80</t>
+          <t>-10.10</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Under 137.5</t>
+          <t>Under 145.5</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Buffalo</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-8.0</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>+0.6</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>+8.60</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Buffalo +8.0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>155.5</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>139.1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-16.40</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Under 155.5</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Harvard</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Columbia</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>+3.5</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>+7.50</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Columbia +4.0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>133.5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-0.50</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Dayton</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>VCU</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-1.5</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>+7.5</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>+9.00</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>VCU +1.5</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>160.2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>12.70</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Over 147.5</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>South Dakota</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nebraska Omaha</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>+3.5</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>+4.2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>+0.70</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>149.5</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>133.2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-16.30</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Under 149.5</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Bradley</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Valparaiso</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-1.6</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>+2.40</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>140.6</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>6.60</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Over 134.0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Queens</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>West Georgia</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-8.0</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-9.5</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-1.50</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>134.6</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-28.40</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>UNC Greensboro</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>VMI</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-7.5</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>+0.2</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>+7.70</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>VMI +7.5</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>154.5</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>115.2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-39.30</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>West Virginia</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>UCF</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>+12.9</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>+16.40</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>UCF +3.5</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>155.3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>15.30</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Over 140.0</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Tennessee St.</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tennessee Martin</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>-10.3</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>-7.80</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tennessee St. -2.5</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>137.5</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-5.50</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Radford</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Presbyterian</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>+1.00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>129.1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-17.40</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Under 146.5</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>South Alabama</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Georgia Southern</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>-5.0</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>+5.0</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>+10.00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Georgia Southern +5.0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>134.8</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-13.20</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Under 148.0</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Saint Peter's</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fairfield</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>-3.5</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>+3.3</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>+6.80</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Fairfield +3.5</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>129.6</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-4.40</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Miami OH</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>+5.5</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>-6.9</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>-12.40</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ohio +5.5</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>159.5</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>164.5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Washington St.</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Portland</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>-6.0</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>-11.8</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>-5.80</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Washington St. -6.0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>151.5</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>145.2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-6.30</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Under 151.5</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Seton Hall</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>St. John's</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>+4.0</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>+6.1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>+2.10</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>165.5</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>29.50</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>North Dakota</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>+3.5</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>+12.0</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>+8.50</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Denver -3.5</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>131.2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>-27.80</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Illinois St.</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Northern Iowa</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>-5.7</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-7.20</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Illinois St. +1.5</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>144.8</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Over 125.0</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>UNLV</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>-10.5</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>+6.8</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>+17.30</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>UNLV +10.5</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>153.5</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>161.2</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>7.70</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Over 153.5</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Morehead St.</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Southeast Missouri St.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>-8.0</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-10.50</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Morehead St. +2.5</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>128.8</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>-12.20</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Under 141.0</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Seattle</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>-9.5</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>+8.1</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>+17.60</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>San Diego +9.5</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>159.3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Over 139.5</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Oklahoma St.</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Houston</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>+13.0</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>+0.8</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-12.20</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Oklahoma St. +13.0</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>170.6</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>20.60</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Virginia Tech</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>-9.5</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>-3.2</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>+6.30</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Virginia Tech +9.5</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>165.6</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>24.10</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Arkansas</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>+4.7</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>+1.70</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>162.0</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>174.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Over 162.0</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Marquette</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Connecticut</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>+9.5</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>+6.5</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-3.00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>166.8</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>23.30</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Arizona St.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>-13.5</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-3.7</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>+9.80</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Arizona St. +13.5</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>171.4</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>24.90</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Kansas St.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>-16.5</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>+15.50</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kansas St. +16.5</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>168.7</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>16.70</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Over 152.0</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Miami FL</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Louisville</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>-2.2</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-3.70</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>157.0</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>177.5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>20.50</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Vanderbilt</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>-5.0</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>-1.1</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>+3.90</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>176.4</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>28.40</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TCU</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Cincinnati</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>-2.5</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>-4.6</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-2.10</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>138.5</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>165.1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>26.60</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Kentucky</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>+7.0</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>-2.3</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-9.30</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kentucky +7.0</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>183.7</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>25.70</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>George Mason</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>Saint Louis</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Loyola Chicago</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>+nan</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>-13.7</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>+nan</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>No Bet</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>144.3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>No Bet</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>+7.5</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>+2.7</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-4.80</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>George Mason +7.5</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>145.5</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>156.4</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>10.90</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Over 145.5</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Purdue</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>-6.5</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>-7.0</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-0.50</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>157.5</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>176.6</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>19.10</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Over 157.5</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Duke</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>-16.0</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>-5.8</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>+10.20</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>North Carolina +16.0</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>180.5</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>35.50</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Alabama</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Auburn</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>-8.5</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>-2.8</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>+5.70</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Auburn +8.5</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>176.5</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>179.2</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>+14.5</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>-1.7</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-16.20</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Colorado +14.5</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>177.8</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>21.80</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>No Bet</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
